--- a/user_total_points.xlsx
+++ b/user_total_points.xlsx
@@ -14,12 +14,153 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>User</t>
   </si>
   <si>
     <t>Points</t>
+  </si>
+  <si>
+    <t>0xN1kU_H4X_!</t>
+  </si>
+  <si>
+    <t>DargoTamber</t>
+  </si>
+  <si>
+    <t>kharayo1x</t>
+  </si>
+  <si>
+    <t>p0tato</t>
+  </si>
+  <si>
+    <t>MrBender</t>
+  </si>
+  <si>
+    <t>SHISHIR GHIMIRE</t>
+  </si>
+  <si>
+    <t>Oju D. Amatya</t>
+  </si>
+  <si>
+    <t>$sudo</t>
+  </si>
+  <si>
+    <t>YoursTruly</t>
+  </si>
+  <si>
+    <t>kinachaiyo</t>
+  </si>
+  <si>
+    <t>Shrenav</t>
+  </si>
+  <si>
+    <t>༒𝙰sʜᴡɪɴ༒</t>
+  </si>
+  <si>
+    <t>luffy</t>
+  </si>
+  <si>
+    <t>MoonLight</t>
+  </si>
+  <si>
+    <t>Iconic_Whisper</t>
+  </si>
+  <si>
+    <t>Nargiza Maharjan</t>
+  </si>
+  <si>
+    <t>Dhiru Piru</t>
+  </si>
+  <si>
+    <t>aayush</t>
+  </si>
+  <si>
+    <t>Yodha</t>
+  </si>
+  <si>
+    <t>Clay69</t>
+  </si>
+  <si>
+    <t>GNU</t>
+  </si>
+  <si>
+    <t>Anmuu</t>
+  </si>
+  <si>
+    <t>thatguysbroke</t>
+  </si>
+  <si>
+    <t>ahlai:3</t>
+  </si>
+  <si>
+    <t>Mandip</t>
+  </si>
+  <si>
+    <t>GUTS</t>
+  </si>
+  <si>
+    <t>Cosmic</t>
+  </si>
+  <si>
+    <t>10y</t>
+  </si>
+  <si>
+    <t>X-night</t>
+  </si>
+  <si>
+    <t>golbeda</t>
+  </si>
+  <si>
+    <t>hello_you0</t>
+  </si>
+  <si>
+    <t>MauLana Rhoades</t>
+  </si>
+  <si>
+    <t>LUCKY_MJ_36457</t>
+  </si>
+  <si>
+    <t>wigglewiggle</t>
+  </si>
+  <si>
+    <t>Adhyan Tamang</t>
+  </si>
+  <si>
+    <t>404Ninjaaa</t>
+  </si>
+  <si>
+    <t>Ansees</t>
+  </si>
+  <si>
+    <t>Abyss_Walker</t>
+  </si>
+  <si>
+    <t>SAKUNA</t>
+  </si>
+  <si>
+    <t>प्रणय</t>
+  </si>
+  <si>
+    <t>Tyrant</t>
+  </si>
+  <si>
+    <t>Shrawan1234</t>
+  </si>
+  <si>
+    <t>Yugal</t>
+  </si>
+  <si>
+    <t>krazy</t>
+  </si>
+  <si>
+    <t>Hexaxe</t>
+  </si>
+  <si>
+    <t>Only Aayush</t>
+  </si>
+  <si>
+    <t>celebbbb</t>
   </si>
 </sst>
 </file>
@@ -377,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -388,6 +529,390 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>1.336614365088055E+18</v>
+      </c>
+      <c r="B31">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/user_total_points.xlsx
+++ b/user_total_points.xlsx
@@ -14,12 +14,153 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>User</t>
   </si>
   <si>
     <t>Points</t>
+  </si>
+  <si>
+    <t>0xN1kU_H4X_!</t>
+  </si>
+  <si>
+    <t>DargoTamber</t>
+  </si>
+  <si>
+    <t>kharayo1x</t>
+  </si>
+  <si>
+    <t>SHISHIR GHIMIRE</t>
+  </si>
+  <si>
+    <t>p0tato</t>
+  </si>
+  <si>
+    <t>MrBender</t>
+  </si>
+  <si>
+    <t>Oju D. Amatya</t>
+  </si>
+  <si>
+    <t>$sudo</t>
+  </si>
+  <si>
+    <t>kinachaiyo</t>
+  </si>
+  <si>
+    <t>YoursTruly</t>
+  </si>
+  <si>
+    <t>Shrenav</t>
+  </si>
+  <si>
+    <t>༒𝙰sʜᴡɪɴ༒</t>
+  </si>
+  <si>
+    <t>luffy</t>
+  </si>
+  <si>
+    <t>MoonLight</t>
+  </si>
+  <si>
+    <t>Iconic_Whisper</t>
+  </si>
+  <si>
+    <t>Nargiza Maharjan</t>
+  </si>
+  <si>
+    <t>Dhiru Piru</t>
+  </si>
+  <si>
+    <t>aayush</t>
+  </si>
+  <si>
+    <t>Yodha</t>
+  </si>
+  <si>
+    <t>Clay69</t>
+  </si>
+  <si>
+    <t>GNU</t>
+  </si>
+  <si>
+    <t>Anmuu</t>
+  </si>
+  <si>
+    <t>thatguysbroke</t>
+  </si>
+  <si>
+    <t>ahlai:3</t>
+  </si>
+  <si>
+    <t>Mandip</t>
+  </si>
+  <si>
+    <t>GUTS</t>
+  </si>
+  <si>
+    <t>Cosmic</t>
+  </si>
+  <si>
+    <t>10y</t>
+  </si>
+  <si>
+    <t>X-night</t>
+  </si>
+  <si>
+    <t>golbeda</t>
+  </si>
+  <si>
+    <t>hello_you0</t>
+  </si>
+  <si>
+    <t>MauLana Rhoades</t>
+  </si>
+  <si>
+    <t>LUCKY_MJ_36457</t>
+  </si>
+  <si>
+    <t>wigglewiggle</t>
+  </si>
+  <si>
+    <t>Adhyan Tamang</t>
+  </si>
+  <si>
+    <t>404Ninjaaa</t>
+  </si>
+  <si>
+    <t>Ansees</t>
+  </si>
+  <si>
+    <t>Abyss_Walker</t>
+  </si>
+  <si>
+    <t>SAKUNA</t>
+  </si>
+  <si>
+    <t>प्रणय</t>
+  </si>
+  <si>
+    <t>Tyrant</t>
+  </si>
+  <si>
+    <t>Shrawan1234</t>
+  </si>
+  <si>
+    <t>Yugal</t>
+  </si>
+  <si>
+    <t>krazy</t>
+  </si>
+  <si>
+    <t>Hexaxe</t>
+  </si>
+  <si>
+    <t>Only Aayush</t>
+  </si>
+  <si>
+    <t>celebbbb</t>
   </si>
 </sst>
 </file>
@@ -377,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -388,6 +529,390 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>9950</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>1.336614365088055E+18</v>
+      </c>
+      <c r="B31">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
